--- a/artfynd/A 53614-2025 artfynd.xlsx
+++ b/artfynd/A 53614-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129491689</v>
       </c>
       <c r="B2" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -774,6 +774,360 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129676811</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Djurröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>398749</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6214484</v>
+      </c>
+      <c r="S3" t="n">
+        <v>68</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fyra bohål under varandra i samma bok mot S på 6-8 m höjd.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129676815</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58100</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Djurröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>398749</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6214484</v>
+      </c>
+      <c r="S4" t="n">
+        <v>68</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129676810</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Djurröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>398749</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6214484</v>
+      </c>
+      <c r="S5" t="n">
+        <v>68</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53614-2025 artfynd.xlsx
+++ b/artfynd/A 53614-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129491689</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>57893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129676811</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>129676815</v>
       </c>
       <c r="B4" t="n">
-        <v>58100</v>
+        <v>58105</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>129676810</v>
       </c>
       <c r="B5" t="n">
-        <v>57724</v>
+        <v>57729</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,6 +1128,319 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129709432</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57893</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Djurröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>398999</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6214629</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Peter Demeyer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Peter Demeyer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129709296</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58452</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Djurröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>398999</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6214629</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Peter Demeyer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Peter Demeyer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129709832</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Djurröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>398999</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6214629</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Peter Demeyer</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Peter Demeyer</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53614-2025 artfynd.xlsx
+++ b/artfynd/A 53614-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129491689</v>
       </c>
       <c r="B2" t="n">
-        <v>57893</v>
+        <v>57894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129676811</v>
       </c>
       <c r="B3" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>129676815</v>
       </c>
       <c r="B4" t="n">
-        <v>58105</v>
+        <v>58106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>129676810</v>
       </c>
       <c r="B5" t="n">
-        <v>57729</v>
+        <v>57730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>129709432</v>
       </c>
       <c r="B6" t="n">
-        <v>57893</v>
+        <v>57894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>129709296</v>
       </c>
       <c r="B7" t="n">
-        <v>58452</v>
+        <v>58453</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>129709832</v>
       </c>
       <c r="B8" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 53614-2025 artfynd.xlsx
+++ b/artfynd/A 53614-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>129676811</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>129676815</v>
       </c>
       <c r="B4" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>129676810</v>
       </c>
       <c r="B5" t="n">
-        <v>57730</v>
+        <v>57731</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>129709432</v>
       </c>
       <c r="B6" t="n">
-        <v>57894</v>
+        <v>57893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>129709296</v>
       </c>
       <c r="B7" t="n">
-        <v>58453</v>
+        <v>58456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>129709832</v>
       </c>
       <c r="B8" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 53614-2025 artfynd.xlsx
+++ b/artfynd/A 53614-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>129676811</v>
       </c>
       <c r="B3" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>129676815</v>
       </c>
       <c r="B4" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>129676810</v>
       </c>
       <c r="B5" t="n">
-        <v>57731</v>
+        <v>57734</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>129709432</v>
       </c>
       <c r="B6" t="n">
-        <v>57893</v>
+        <v>57896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>129709296</v>
       </c>
       <c r="B7" t="n">
-        <v>58456</v>
+        <v>58459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>129709832</v>
       </c>
       <c r="B8" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 53614-2025 artfynd.xlsx
+++ b/artfynd/A 53614-2025 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>129676815</v>
       </c>
       <c r="B4" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>129709432</v>
       </c>
       <c r="B6" t="n">
-        <v>57896</v>
+        <v>57897</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>129709296</v>
       </c>
       <c r="B7" t="n">
-        <v>58459</v>
+        <v>58460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>129709832</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 53614-2025 artfynd.xlsx
+++ b/artfynd/A 53614-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1441,6 +1441,129 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131347217</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58041</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Djurröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>398995</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6214584</v>
+      </c>
+      <c r="S9" t="n">
+        <v>67</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53614-2025 artfynd.xlsx
+++ b/artfynd/A 53614-2025 artfynd.xlsx
@@ -1446,7 +1446,7 @@
         <v>131347217</v>
       </c>
       <c r="B9" t="n">
-        <v>58041</v>
+        <v>58043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 53614-2025 artfynd.xlsx
+++ b/artfynd/A 53614-2025 artfynd.xlsx
@@ -1446,7 +1446,7 @@
         <v>131347217</v>
       </c>
       <c r="B9" t="n">
-        <v>58043</v>
+        <v>58044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 53614-2025 artfynd.xlsx
+++ b/artfynd/A 53614-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1446,7 +1446,7 @@
         <v>131347217</v>
       </c>
       <c r="B9" t="n">
-        <v>58044</v>
+        <v>58045</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,6 +1563,240 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131480333</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58045</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Djurröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>398969</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6214607</v>
+      </c>
+      <c r="S10" t="n">
+        <v>64</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131480330</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57882</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Djurröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>398969</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6214607</v>
+      </c>
+      <c r="S11" t="n">
+        <v>64</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53614-2025 artfynd.xlsx
+++ b/artfynd/A 53614-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1798,6 +1798,601 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131503582</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57182</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100038</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsduva</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Columba oenas</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Djurröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>398969</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6214607</v>
+      </c>
+      <c r="S12" t="n">
+        <v>64</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131503612</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58321</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Djurröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>398969</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6214607</v>
+      </c>
+      <c r="S13" t="n">
+        <v>64</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131503618</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58569</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Djurröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>398969</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6214607</v>
+      </c>
+      <c r="S14" t="n">
+        <v>64</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131503616</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58535</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Djurröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>398969</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6214607</v>
+      </c>
+      <c r="S15" t="n">
+        <v>64</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131503589</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57885</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Djurröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>398969</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6214607</v>
+      </c>
+      <c r="S16" t="n">
+        <v>64</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53614-2025 artfynd.xlsx
+++ b/artfynd/A 53614-2025 artfynd.xlsx
@@ -1446,7 +1446,7 @@
         <v>131347217</v>
       </c>
       <c r="B9" t="n">
-        <v>58045</v>
+        <v>58048</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>131480333</v>
       </c>
       <c r="B10" t="n">
-        <v>58045</v>
+        <v>58048</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131480330</v>
       </c>
       <c r="B11" t="n">
-        <v>57882</v>
+        <v>57885</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>131503582</v>
       </c>
       <c r="B12" t="n">
-        <v>57182</v>
+        <v>57185</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>131503612</v>
       </c>
       <c r="B13" t="n">
-        <v>58321</v>
+        <v>58324</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>131503618</v>
       </c>
       <c r="B14" t="n">
-        <v>58569</v>
+        <v>58572</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>131503616</v>
       </c>
       <c r="B15" t="n">
-        <v>58535</v>
+        <v>58538</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>131503589</v>
       </c>
       <c r="B16" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 53614-2025 artfynd.xlsx
+++ b/artfynd/A 53614-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1446,7 +1446,7 @@
         <v>131347217</v>
       </c>
       <c r="B9" t="n">
-        <v>58048</v>
+        <v>58049</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>131480333</v>
       </c>
       <c r="B10" t="n">
-        <v>58048</v>
+        <v>58049</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131480330</v>
       </c>
       <c r="B11" t="n">
-        <v>57885</v>
+        <v>57886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>131503582</v>
       </c>
       <c r="B12" t="n">
-        <v>57185</v>
+        <v>57186</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>131503612</v>
       </c>
       <c r="B13" t="n">
-        <v>58324</v>
+        <v>58325</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>131503618</v>
       </c>
       <c r="B14" t="n">
-        <v>58572</v>
+        <v>58573</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>131503616</v>
       </c>
       <c r="B15" t="n">
-        <v>58538</v>
+        <v>58539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>131503589</v>
       </c>
       <c r="B16" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,6 +2392,134 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131573492</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57905</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Djurröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>398969</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6214607</v>
+      </c>
+      <c r="S17" t="n">
+        <v>64</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Noteras mellan 8-9 och mellan 11-12.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53614-2025 artfynd.xlsx
+++ b/artfynd/A 53614-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131503582</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131573329</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1038,6 +1053,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129676811</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1157,6 +1177,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131503589</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1272,6 +1297,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129676810</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1387,6 +1417,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131480330</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1506,6 +1541,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131503612</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1621,6 +1661,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129676815</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1740,6 +1785,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131572976</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1849,6 +1899,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129468184</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1950,6 +2005,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129491689</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2051,6 +2111,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129709432</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2174,6 +2239,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131347217</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2293,6 +2363,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131480333</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2394,6 +2469,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129709832</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2513,6 +2593,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131503616</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2632,6 +2717,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131503618</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2743,8 +2833,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129709296</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>